--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -1,33 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>NAGUANAGUA</t>
+  </si>
+  <si>
+    <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>PCP CARLOS GONZALEZ</t>
+  </si>
+  <si>
+    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+  </si>
+  <si>
+    <t>TIPO A</t>
+  </si>
+  <si>
+    <t>NÚMERO DE FACTURA INCORRECTO</t>
+  </si>
+  <si>
+    <t>SIN FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>20260504113349</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +125,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,84 +419,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -61,34 +61,55 @@
     <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
   </si>
   <si>
-    <t>864</t>
+    <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+  </si>
+  <si>
+    <t>663</t>
   </si>
   <si>
     <t>2026-05-02</t>
   </si>
   <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
     <t>PCP CARLOS GONZALEZ</t>
   </si>
   <si>
+    <t>PCP ANDRES ARCILA</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
+    <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
     <t>NÚMERO DE FACTURA INCORRECTO</t>
   </si>
   <si>
+    <t>FALTA NÚMERO DE CÉDULA DEL SPCP</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
     <t>NINGUNA</t>
   </si>
   <si>
     <t>20260504113349</t>
+  </si>
+  <si>
+    <t>HIST_20260504163237</t>
   </si>
 </sst>
 </file>
@@ -420,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -471,38 +492,79 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
+      <c r="C2">
+        <v>864</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+      <c r="H3" t="s">
         <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>NAGUANAGUA</t>
   </si>
   <si>
@@ -64,7 +67,10 @@
     <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
   </si>
   <si>
-    <t>663</t>
+    <t>ADOLFO'S VICAR, C.A</t>
+  </si>
+  <si>
+    <t>0000</t>
   </si>
   <si>
     <t>2026-05-02</t>
@@ -76,27 +82,42 @@
     <t>RECEPCION</t>
   </si>
   <si>
+    <t>DEVOLUCION</t>
+  </si>
+  <si>
     <t>PCP CARLOS GONZALEZ</t>
   </si>
   <si>
     <t>PCP ANDRES ARCILA</t>
   </si>
   <si>
+    <t>PCP JOSE MALUENGA</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
     <t>FALTA SELLO, FIRMA O CÉDULA.</t>
   </si>
   <si>
+    <t>FISCALIZACIÓN A DESTIEMPO</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
     <t>NÚMERO DE FACTURA INCORRECTO</t>
   </si>
   <si>
     <t>FALTA NÚMERO DE CÉDULA DEL SPCP</t>
   </si>
   <si>
+    <t>NO CULMINÓ PROCESO DE FISCALIZACIÓN, NO INGRESÓ EN LA APP EL DOCUMENTO A TIEMPO</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -110,6 +131,12 @@
   </si>
   <si>
     <t>HIST_20260504163237</t>
+  </si>
+  <si>
+    <t>ID_20260505092906</t>
+  </si>
+  <si>
+    <t>INC_092906.png</t>
   </si>
 </sst>
 </file>
@@ -441,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,87 +511,134 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>864</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>663</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" t="s">
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -1,163 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>NAGUANAGUA</t>
-  </si>
-  <si>
-    <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
-  </si>
-  <si>
-    <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
-  </si>
-  <si>
-    <t>ADOLFO'S VICAR, C.A</t>
-  </si>
-  <si>
-    <t>0000</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>DEVOLUCION</t>
-  </si>
-  <si>
-    <t>PCP CARLOS GONZALEZ</t>
-  </si>
-  <si>
-    <t>PCP ANDRES ARCILA</t>
-  </si>
-  <si>
-    <t>PCP JOSE MALUENGA</t>
-  </si>
-  <si>
-    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-  </si>
-  <si>
-    <t>FALTA SELLO, FIRMA O CÉDULA.</t>
-  </si>
-  <si>
-    <t>FISCALIZACIÓN A DESTIEMPO</t>
-  </si>
-  <si>
-    <t>TIPO A</t>
-  </si>
-  <si>
-    <t>TIPO B</t>
-  </si>
-  <si>
-    <t>NÚMERO DE FACTURA INCORRECTO</t>
-  </si>
-  <si>
-    <t>FALTA NÚMERO DE CÉDULA DEL SPCP</t>
-  </si>
-  <si>
-    <t>NO CULMINÓ PROCESO DE FISCALIZACIÓN, NO INGRESÓ EN LA APP EL DOCUMENTO A TIEMPO</t>
-  </si>
-  <si>
-    <t>SIN FOTO</t>
-  </si>
-  <si>
-    <t>SIN_FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>20260504113349</t>
-  </si>
-  <si>
-    <t>HIST_20260504163237</t>
-  </si>
-  <si>
-    <t>ID_20260505092906</t>
-  </si>
-  <si>
-    <t>INC_092906.png</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -172,14 +52,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -467,181 +415,409 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>864</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PCP CARLOS GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NÚMERO DE FACTURA INCORRECTO</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>20260504113349</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>864</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>663</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PCP ANDRES ARCILA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FALTA NÚMERO DE CÉDULA DEL SPCP</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>HIST_20260504163237</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>663</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PCP JOSE MALUENGA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NO CULMINÓ PROCESO DE FISCALIZACIÓN, NO INGRESÓ EN LA APP EL DOCUMENTO A TIEMPO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260505092906</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_092906.png</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>664</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SPCP CARLOS GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ERROR EN PESAJE DE TARA DE OCUMO CRIOLLO, 800GR DE DIFERENCIA</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260506100042</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PRODUCTOS FRESCOS PROFRESCA, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B000028010</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SPCP JOSE MALUENGA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FACTURA BORROSA, NO SE VISUALIZA LA CANTIDAD DE LOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" t="s">
-        <v>40</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260506101749</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,40 +496,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
+          <t>ADOLFO'S VICAR, C.A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PCP CARLOS GONZALEZ</t>
+          <t>PCP JOSE MALUENGA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NÚMERO DE FACTURA INCORRECTO</t>
+          <t>NO CULMINÓ PROCESO DE FISCALIZACIÓN, NO INGRESÓ EN LA APP EL DOCUMENTO A TIEMPO</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -544,7 +537,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SIN FOTO</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -554,7 +547,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>20260504113349</t>
+          <t>ID_20260505092906</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>INC_092906.png</t>
         </is>
       </c>
     </row>
@@ -570,11 +568,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -584,26 +582,26 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PCP ANDRES ARCILA</t>
+          <t>SPCP CARLOS GONZALEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+          <t>ERROR DE KG EN TARA.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FALTA NÚMERO DE CÉDULA DEL SPCP</t>
+          <t>ERROR EN PESAJE DE TARA DE OCUMO CRIOLLO, 800GR DE DIFERENCIA</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -612,14 +610,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>RECUPERACIÓN</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HIST_20260504163237</t>
-        </is>
-      </c>
+          <t>ID_20260506100042</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,40 +628,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR, C.A</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+          <t>PRODUCTOS FRESCOS PROFRESCA, C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B000028010</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PCP JOSE MALUENGA</t>
+          <t>SPCP JOSE MALUENGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FISCALIZACIÓN A DESTIEMPO</t>
+          <t>DOCUMENTO NO LEGIBLE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NO CULMINÓ PROCESO DE FISCALIZACIÓN, NO INGRESÓ EN LA APP EL DOCUMENTO A TIEMPO</t>
+          <t>FACTURA BORROSA, NO SE VISUALIZA LA CANTIDAD DE LOS PRODUCTOS</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -680,14 +681,10 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260505092906</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>INC_092906.png</t>
-        </is>
-      </c>
+          <t>ID_20260506101749</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -697,15 +694,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>664</v>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -715,26 +714,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SPCP CARLOS GONZALEZ</t>
+          <t>SUB STEVEN SERVET</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ERROR EN PESAJE DE TARA DE OCUMO CRIOLLO, 800GR DE DIFERENCIA</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>1.14</v>
+          <t>NÚMERO DE CONTROL INCORRECTO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -743,14 +742,15 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>RECUPERACIÓN</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260506100042</t>
-        </is>
-      </c>
+          <t>ID_20260507080035</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PRODUCTOS FRESCOS PROFRESCA, C.A.</t>
+          <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B000028010</t>
+          <t>0002360</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DOCUMENTO NO LEGIBLE</t>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO E</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FACTURA BORROSA, NO SE VISUALIZA LA CANTIDAD DE LOS PRODUCTOS</t>
+          <t xml:space="preserve">SIN AUTORIZACIÓN PARA INICIAR RECEPCIÓN </t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -813,9 +813,142 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260506101749</t>
-        </is>
-      </c>
+          <t>ID_20260507082412</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C,A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SPCP CARLOS GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NÚMERO DE FACTURA INCORRECTO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>20260504113349</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SPCP ANDRES ARCILA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FALTA NÚMERO DE CÉDULA DEL SPCP</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>HIST_20260504163237</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,72 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AGRICOLA CORVARA, C.A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>031080</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUB REINALDO SILVA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NÚMERO DE FACTURA INCORRECTO</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260507141122</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,142 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13626</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SPCP CARLOS GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RESPONSABLE NO INGRESÓ SKU DE CHAYOTA EN LA APP</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260511110301</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS, C.A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6334</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RECIBIDOR FÉLIX RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SE RECIBE 227.6KG DE AGUACATE, EN FACTURA 232.8KG. DIFERENCIA: 5.2KG FALTANTES</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>00274005.jpeg</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260511124223</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>INC_124223.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -600,7 +614,7 @@
           <t>ERROR EN PESAJE DE TARA DE OCUMO CRIOLLO, 800GR DE DIFERENCIA</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>1.14</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,7 +632,6 @@
           <t>ID_20260506100042</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,7 +697,6 @@
           <t>ID_20260506101749</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,7 +762,6 @@
           <t>ID_20260507080035</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -816,7 +827,6 @@
           <t>ID_20260507082412</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -882,7 +892,6 @@
           <t>20260504113349</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -948,7 +957,6 @@
           <t>HIST_20260504163237</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1014,7 +1022,6 @@
           <t>ID_20260507141122</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1080,7 +1087,6 @@
           <t>ID_20260511110301</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,7 +1134,7 @@
           <t>SE RECIBE 227.6KG DE AGUACATE, EN FACTURA 232.8KG. DIFERENCIA: 5.2KG FALTANTES</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="2" t="n">
         <v>15.55</v>
       </c>
       <c r="K11" t="inlineStr">

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,7 +600,7 @@
           <t>ERROR EN PESAJE DE TARA DE OCUMO CRIOLLO, 800GR DE DIFERENCIA</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>1.14</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -632,6 +618,7 @@
           <t>ID_20260506100042</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,6 +684,7 @@
           <t>ID_20260506101749</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -762,6 +750,7 @@
           <t>ID_20260507080035</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,6 +816,7 @@
           <t>ID_20260507082412</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -892,6 +882,7 @@
           <t>20260504113349</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -957,6 +948,7 @@
           <t>HIST_20260504163237</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1022,6 +1014,7 @@
           <t>ID_20260507141122</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1087,6 +1080,7 @@
           <t>ID_20260511110301</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1134,7 +1128,7 @@
           <t>SE RECIBE 227.6KG DE AGUACATE, EN FACTURA 232.8KG. DIFERENCIA: 5.2KG FALTANTES</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" t="n">
         <v>15.55</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -1157,6 +1151,72 @@
           <t>INC_124223.png</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>33268</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SPCP JOSE MALUENGA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ERROR EN TARA DE LIMÓN, 100GR DEMÁS</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260513105028</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,76 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>000794</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SUB STEVEN SERVET</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SE VISUALIZA EXCEDENTE DE 6.6KG DE PATILLA</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO.png</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>EXCEDENTES</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260513135336</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>INC_135336.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,6 +1285,76 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>INC_135336.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13661</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>RECIBIDOR OMAR BARRETO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SE RECIBE 61.6 KG DE CEDANO, EN FACTURA 63.9KG. DIFERENCIA: 2.3KG FALTANTES</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>00227146.jpeg</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260513164421</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>INC_164421.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,8 +519,10 @@
           <t>ADOLFO'S VICAR, C.A</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -587,8 +589,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>664</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1436,6 +1440,76 @@
       <c r="N15" t="inlineStr">
         <is>
           <t>INC_095700_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FRUMIX,C.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>00009734</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>RECIBIDOR OMAR BARRETO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SE RECIBEN 18.6KG DE MANDARINA IMPORTADA, EN FACTURA 19KG. DIFERENCIA: 400GR DE MANDARINA</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>COB_135132_0.jpeg</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ID_20260514135132</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>INC_135132_0.png INC_135132_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/NAGUANAGUA.xlsx
+++ b/cuadros/MAYO/NAGUANAGUA.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,6 +1513,71 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13682</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUB STEVEN SERVET</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INGRESA SKU INCORRECTO EN LA APP.</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ID_20260515164721</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
